--- a/branches/jose/StructureDefinition-MedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-MedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-23T12:05:04+00:00</t>
+    <t>2022-08-23T16:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,7 +249,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Element {http://example.com/fhir/example/StructureDefinition/descriptor}
+    <t xml:space="preserve">Element {http://example.com/fhir/example/StructureDefinition/II}
 </t>
   </si>
   <si>
@@ -259,7 +259,7 @@
     <t>MedicinalProduct.CombinedPharmaceuticalDoseForm</t>
   </si>
   <si>
-    <t xml:space="preserve">Element {http://example.com/fhir/example/StructureDefinition/coded}
+    <t xml:space="preserve">Element {http://example.com/fhir/example/StructureDefinition/CD}
 </t>
   </si>
   <si>
@@ -275,7 +275,7 @@
     <t>MedicinalProduct.SpecialMeasures</t>
   </si>
   <si>
-    <t xml:space="preserve">Element {http://example.com/fhir/example/StructureDefinition/text}
+    <t xml:space="preserve">Element {http://example.com/fhir/example/StructureDefinition/ST}
 </t>
   </si>
   <si>
@@ -297,14 +297,14 @@
     <t>MedicinalProduct.Header</t>
   </si>
   <si>
-    <t xml:space="preserve">BackboneElement {http://example.com/fhir/example/StructureDefinition/grouping}
+    <t xml:space="preserve">BackboneElement {http://example.com/fhir/example/StructureDefinition/class}
 </t>
   </si>
   <si>
     <t>9.2.2.10</t>
   </si>
   <si>
-    <t>MedicinalProduct.Header.descriptor</t>
+    <t>MedicinalProduct.Header.II</t>
   </si>
   <si>
     <t>9.2.2.10.2</t>
@@ -332,7 +332,7 @@
     <t>9.2.2.10.5</t>
   </si>
   <si>
-    <t>MedicinalProduct.Header.VersionSetdescriptor</t>
+    <t>MedicinalProduct.Header.VersionSetII</t>
   </si>
   <si>
     <t>9.2.2.10.6</t>

--- a/branches/jose/StructureDefinition-MedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-MedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-23T16:03:23+00:00</t>
+    <t>2022-08-23T16:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/jose/StructureDefinition-MedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-MedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-23T16:03:37+00:00</t>
+    <t>2022-08-24T08:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/jose/StructureDefinition-MedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-MedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T08:06:58+00:00</t>
+    <t>2022-08-24T08:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
